--- a/exports/DELHIVERY_full_report.xlsx
+++ b/exports/DELHIVERY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>22.23</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44729.38541666666</v>
+        <v>44729.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="I2" t="n">
         <v>471.204166105</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.94</v>
+        <v>-10.19</v>
       </c>
       <c r="L2" t="n">
-        <v>8.27</v>
+        <v>12.48</v>
       </c>
       <c r="M2" t="n">
         <v>3.66</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.86</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>509.95</v>
+        <v>522.8</v>
       </c>
       <c r="I3" t="n">
         <v>515.4314767439449</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.5</v>
+        <v>-11.23</v>
       </c>
       <c r="L3" t="n">
         <v>12.77</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.09</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>633.65</v>
+        <v>620</v>
       </c>
       <c r="I4" t="n">
         <v>624.6279739237563</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>21.2</v>
+        <v>18.59</v>
       </c>
       <c r="L4" t="n">
         <v>3.2</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.65</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>595.2</v>
+        <v>606.5</v>
       </c>
       <c r="I5" t="n">
         <v>599.1671850473919</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>70</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="L5" t="n">
         <v>6.13</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44844.55208333334</v>
+        <v>44845.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>575</v>
+        <v>556.7</v>
       </c>
       <c r="I6" t="n">
         <v>557.9607410310867</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.19</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>5.72</v>
+        <v>8.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.17</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.13</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>338.8</v>
+        <v>348</v>
       </c>
       <c r="I7" t="n">
         <v>347.3416032851912</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K7" t="n">
-        <v>39.14</v>
+        <v>37.49</v>
       </c>
       <c r="L7" t="n">
         <v>4.17</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.73</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>343</v>
+        <v>334.3</v>
       </c>
       <c r="I8" t="n">
         <v>339.7751900255408</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.44</v>
+        <v>-3.94</v>
       </c>
       <c r="L8" t="n">
-        <v>4.53</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
         <v>0.82</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.63</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44946.55208333334</v>
+        <v>44949.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>306.65</v>
+        <v>325.3</v>
       </c>
       <c r="I9" t="n">
         <v>323.5895854115689</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K9" t="n">
-        <v>8.27</v>
+        <v>2.69</v>
       </c>
       <c r="L9" t="n">
         <v>3.05</v>
@@ -954,7 +1061,7 @@
         <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>5.43</v>
       </c>
       <c r="O9" t="n">
         <v>-3.91</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.82</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>306</v>
+        <v>297.6</v>
       </c>
       <c r="I10" t="n">
         <v>300.7123455114697</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.93</v>
+        <v>-8.52</v>
       </c>
       <c r="L10" t="n">
-        <v>6.24</v>
+        <v>10.54</v>
       </c>
       <c r="M10" t="n">
         <v>0.8</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>9.91</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>319.1</v>
+        <v>327.35</v>
       </c>
       <c r="I11" t="n">
         <v>323.7488192533717</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.22</v>
+        <v>-10</v>
       </c>
       <c r="L11" t="n">
-        <v>9.539999999999999</v>
+        <v>10.52</v>
       </c>
       <c r="M11" t="n">
         <v>2.41</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.6</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44995.38541666666</v>
+        <v>44995.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>324.35</v>
+        <v>320.9</v>
       </c>
       <c r="I12" t="n">
         <v>322.071545011916</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.92</v>
+        <v>-1.97</v>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="M12" t="n">
         <v>0.54</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.63</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45036.55208333334</v>
+        <v>45037.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>337.15</v>
+        <v>351.55</v>
       </c>
       <c r="I13" t="n">
         <v>341.3475960824982</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.06</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>7.01</v>
+        <v>11.06</v>
       </c>
       <c r="M13" t="n">
         <v>0.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="O13" t="n">
         <v>-3.37</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>421.95</v>
+        <v>419</v>
       </c>
       <c r="I14" t="n">
         <v>419.0405538829414</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>144</v>
+        <v>144.1666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>20.03</v>
+        <v>19.19</v>
       </c>
       <c r="L14" t="n">
         <v>4.69</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>199</v>
+        <v>200</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.36</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45209.38541666666</v>
+        <v>45209.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>427.25</v>
+        <v>433.5</v>
       </c>
       <c r="I15" t="n">
         <v>429.1231121178477</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.97</v>
+        <v>-3.46</v>
       </c>
       <c r="L15" t="n">
         <v>6.16</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.03</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45222.38541666666</v>
+        <v>45222.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>416</v>
+        <v>415.5</v>
       </c>
       <c r="I16" t="n">
         <v>415.5606411394801</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.04</v>
+        <v>-4.15</v>
       </c>
       <c r="L16" t="n">
-        <v>4.27</v>
+        <v>4.82</v>
       </c>
       <c r="M16" t="n">
         <v>1.25</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.49</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45281.38541666666</v>
+        <v>45281.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>383.85</v>
+        <v>387.1</v>
       </c>
       <c r="I17" t="n">
         <v>384.6544898654121</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>58.83333333333334</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
-        <v>7.62</v>
+        <v>6.84</v>
       </c>
       <c r="L17" t="n">
         <v>3.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>398.05</v>
+        <v>393.3</v>
       </c>
       <c r="I18" t="n">
         <v>396.8596691727422</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>2.83</v>
+        <v>1.6</v>
       </c>
       <c r="L18" t="n">
         <v>2.48</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>401.3</v>
+        <v>430.7</v>
       </c>
       <c r="I19" t="n">
         <v>411.9874517870147</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.03</v>
+        <v>-9.51</v>
       </c>
       <c r="L19" t="n">
-        <v>2.96</v>
+        <v>10.09</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9</v>
+        <v>2.17</v>
       </c>
       <c r="N19" t="n">
-        <v>2.81</v>
+        <v>6.95</v>
       </c>
       <c r="O19" t="n">
         <v>-2.17</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.31</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>441.75</v>
+        <v>428.85</v>
       </c>
       <c r="I20" t="n">
         <v>433.3253540157707</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>2.57</v>
+        <v>-0.43</v>
       </c>
       <c r="L20" t="n">
         <v>5.72</v>
@@ -1581,7 +1820,7 @@
         <v>0.33</v>
       </c>
       <c r="N20" t="n">
-        <v>4.28</v>
+        <v>4.92</v>
       </c>
       <c r="O20" t="n">
         <v>6.95</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.47</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45392.55208333334</v>
+        <v>45394.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>450.4</v>
+        <v>470.25</v>
       </c>
       <c r="I21" t="n">
         <v>468.32947489132</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.03</v>
+        <v>-9.65</v>
       </c>
       <c r="L21" t="n">
         <v>13.09</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.02</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>454.9</v>
+        <v>431.1</v>
       </c>
       <c r="I22" t="n">
         <v>435.3596747919736</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.26</v>
+        <v>-8.33</v>
       </c>
       <c r="L22" t="n">
-        <v>7.27</v>
+        <v>8.33</v>
       </c>
       <c r="M22" t="n">
         <v>1.27</v>
       </c>
       <c r="N22" t="n">
-        <v>2.36</v>
+        <v>5.23</v>
       </c>
       <c r="O22" t="n">
         <v>3.04</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.9</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45456.55208333334</v>
+        <v>45457.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>393.45</v>
+        <v>407.1</v>
       </c>
       <c r="I23" t="n">
         <v>398.3249943231863</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>8.73</v>
+        <v>5.57</v>
       </c>
       <c r="L23" t="n">
         <v>6.7</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>7.68</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45483.55208333334</v>
+        <v>45484.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>386.95</v>
+        <v>378.25</v>
       </c>
       <c r="I24" t="n">
         <v>385.048274797026</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.95</v>
+        <v>-7.09</v>
       </c>
       <c r="L24" t="n">
-        <v>5.17</v>
+        <v>7.5</v>
       </c>
       <c r="M24" t="n">
         <v>0.91</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>6.97</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>378.3</v>
+        <v>395.25</v>
       </c>
       <c r="I25" t="n">
         <v>392.9019014635376</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.01</v>
+        <v>-4.49</v>
       </c>
       <c r="L25" t="n">
-        <v>3.23</v>
+        <v>5.42</v>
       </c>
       <c r="M25" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1</v>
+        <v>4.76</v>
       </c>
       <c r="O25" t="n">
         <v>-2.27</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>411.9</v>
+        <v>410.5</v>
       </c>
       <c r="I26" t="n">
         <v>411.0299663257694</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K26" t="n">
-        <v>4.21</v>
+        <v>3.86</v>
       </c>
       <c r="L26" t="n">
         <v>3.81</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.39</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45554.55208333334</v>
+        <v>45555.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>426.6</v>
+        <v>430</v>
       </c>
       <c r="I27" t="n">
         <v>428.5392262951526</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.92</v>
+        <v>-4.75</v>
       </c>
       <c r="L27" t="n">
         <v>5.32</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>4.84</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45566.38541666666</v>
+        <v>45566.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>424.3</v>
+        <v>419.2</v>
       </c>
       <c r="I28" t="n">
         <v>419.6187740456797</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.33</v>
+        <v>-2.51</v>
       </c>
       <c r="L28" t="n">
-        <v>1.86</v>
+        <v>2.79</v>
       </c>
       <c r="M28" t="n">
         <v>0.06</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.92</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45614.55208333334</v>
+        <v>45615.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>327.9</v>
+        <v>350</v>
       </c>
       <c r="I29" t="n">
         <v>349.378101573541</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>21.78</v>
+        <v>16.51</v>
       </c>
       <c r="L29" t="n">
         <v>1.93</v>
@@ -2094,7 +2441,7 @@
         <v>2.54</v>
       </c>
       <c r="N29" t="n">
-        <v>3.11</v>
+        <v>4.61</v>
       </c>
       <c r="O29" t="n">
         <v>-1.41</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.77</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>372.25</v>
+        <v>363.4</v>
       </c>
       <c r="I30" t="n">
         <v>369.9857445751497</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K30" t="n">
-        <v>6.36</v>
+        <v>3.83</v>
       </c>
       <c r="L30" t="n">
         <v>6.49</v>
       </c>
       <c r="M30" t="n">
-        <v>1.29</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="O30" t="n">
         <v>4.61</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45677.38541666666</v>
+        <v>45677.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>342.6</v>
+        <v>343.8</v>
       </c>
       <c r="I31" t="n">
         <v>343.3051592717549</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>5.72</v>
+        <v>5.39</v>
       </c>
       <c r="L31" t="n">
         <v>1.13</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>6.49</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45678.55208333334</v>
+        <v>45679.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>328.8</v>
+        <v>317</v>
       </c>
       <c r="I32" t="n">
         <v>321.4734470912549</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.36</v>
+        <v>-7.8</v>
       </c>
       <c r="L32" t="n">
-        <v>4.71</v>
+        <v>9.15</v>
       </c>
       <c r="M32" t="n">
         <v>0.06</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45735.38541666666</v>
+        <v>45735.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>259.04</v>
+        <v>261.29</v>
       </c>
       <c r="I33" t="n">
         <v>259.8097531928357</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>18.28</v>
+        <v>17.57</v>
       </c>
       <c r="L33" t="n">
         <v>4.89</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.31</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45755.55208333334</v>
+        <v>45756.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>249.45</v>
+        <v>245.3</v>
       </c>
       <c r="I34" t="n">
         <v>247.8735092980485</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.53</v>
+        <v>-6.12</v>
       </c>
       <c r="L34" t="n">
         <v>8.720000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.52</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>263</v>
+        <v>280.75</v>
       </c>
       <c r="I35" t="n">
         <v>273.1603841616153</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K35" t="n">
-        <v>-7.22</v>
+        <v>-14.45</v>
       </c>
       <c r="L35" t="n">
-        <v>7.5</v>
+        <v>15.04</v>
       </c>
       <c r="M35" t="n">
         <v>2.44</v>
       </c>
       <c r="N35" t="n">
-        <v>4.52</v>
+        <v>6.79</v>
       </c>
       <c r="O35" t="n">
         <v>-2.39</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.87</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45827.38541666666</v>
+        <v>45827.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>357.35</v>
+        <v>353.05</v>
       </c>
       <c r="I36" t="n">
         <v>353.2090262072232</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>27.28</v>
+        <v>25.75</v>
       </c>
       <c r="L36" t="n">
         <v>6.61</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.78</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>360.45</v>
+        <v>378.45</v>
       </c>
       <c r="I37" t="n">
         <v>372.7777037726578</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.1</v>
+        <v>-7.19</v>
       </c>
       <c r="L37" t="n">
-        <v>2.69</v>
+        <v>7.35</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>1.39</v>
+        <v>5.1</v>
       </c>
       <c r="O37" t="n">
         <v>-3.19</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45866.55208333334</v>
+        <v>45867.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>428.9</v>
+        <v>421.4</v>
       </c>
       <c r="I38" t="n">
         <v>423.028991104164</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>13.33</v>
+        <v>11.35</v>
       </c>
       <c r="L38" t="n">
         <v>4.27</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>6.2</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>426</v>
+        <v>433.6</v>
       </c>
       <c r="I39" t="n">
         <v>433.5938285306231</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.09</v>
+        <v>-2.9</v>
       </c>
       <c r="L39" t="n">
-        <v>2.17</v>
+        <v>3.88</v>
       </c>
       <c r="M39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="N39" t="n">
         <v>4.16</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.26</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>469</v>
+        <v>460.2</v>
       </c>
       <c r="I40" t="n">
         <v>463.4219565997182</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K40" t="n">
-        <v>8.16</v>
+        <v>6.13</v>
       </c>
       <c r="L40" t="n">
         <v>2.1</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.53</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>456.6</v>
+        <v>461.8</v>
       </c>
       <c r="I41" t="n">
         <v>460.5771025280793</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>0.78</v>
+        <v>-0.35</v>
       </c>
       <c r="L41" t="n">
         <v>1.9</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.68</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>486</v>
+        <v>453.1</v>
       </c>
       <c r="I42" t="n">
         <v>459.71176739236</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>5.24</v>
+        <v>-1.88</v>
       </c>
       <c r="L42" t="n">
-        <v>3.43</v>
+        <v>4.04</v>
       </c>
       <c r="M42" t="n">
-        <v>0.68</v>
+        <v>3.29</v>
       </c>
       <c r="N42" t="n">
-        <v>3.13</v>
+        <v>10.21</v>
       </c>
       <c r="O42" t="n">
         <v>5.53</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>411.4</v>
+        <v>415.05</v>
       </c>
       <c r="I43" t="n">
         <v>415.0092977993464</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K43" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L43" t="n">
         <v>3.73</v>
       </c>
       <c r="M43" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="N43" t="n">
         <v>3.82</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.04</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>404.05</v>
+        <v>389.5</v>
       </c>
       <c r="I44" t="n">
         <v>403.9893245657562</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.65</v>
+        <v>-6.16</v>
       </c>
       <c r="L44" t="n">
-        <v>2.95</v>
+        <v>7.73</v>
       </c>
       <c r="M44" t="n">
         <v>0.72</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.8</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>399.4</v>
+        <v>403.6</v>
       </c>
       <c r="I45" t="n">
         <v>403.0902189639723</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.54</v>
+        <v>-3.62</v>
       </c>
       <c r="L45" t="n">
         <v>5.01</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.27</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>429</v>
+        <v>416.05</v>
       </c>
       <c r="I46" t="n">
         <v>421.2763950067804</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K46" t="n">
-        <v>6.29</v>
+        <v>3.08</v>
       </c>
       <c r="L46" t="n">
         <v>1.21</v>
@@ -3063,7 +3614,7 @@
         <v>5.34</v>
       </c>
       <c r="N46" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="O46" t="n">
         <v>1.89</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.4</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>417</v>
+        <v>431.5</v>
       </c>
       <c r="I47" t="n">
         <v>428.2306926267142</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.23</v>
+        <v>-3.71</v>
       </c>
       <c r="L47" t="n">
-        <v>3.47</v>
+        <v>3.83</v>
       </c>
       <c r="M47" t="n">
         <v>2.19</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>476.2</v>
+        <v>451.45</v>
       </c>
       <c r="I48" t="n">
         <v>452.2083552008912</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K48" t="n">
-        <v>10.36</v>
+        <v>4.62</v>
       </c>
       <c r="L48" t="n">
         <v>4.65</v>
@@ -3177,7 +3752,7 @@
         <v>2.55</v>
       </c>
       <c r="N48" t="n">
-        <v>3.51</v>
+        <v>4.03</v>
       </c>
       <c r="O48" t="n">
         <v>3.12</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.02</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>452.7</v>
+        <v>458.5</v>
       </c>
       <c r="I49" t="n">
         <v>456.874748621264</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.28</v>
+        <v>-1.56</v>
       </c>
       <c r="L49" t="n">
         <v>4.76</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>4.92</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46220.55208333334</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>491.95</v>
+        <v>486</v>
       </c>
       <c r="I50" t="n">
         <v>489.5996672511403</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K50" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
         <v>1.31</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="N50" t="n">
         <v>3.09</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.54</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>451.05</v>
+        <v>464.95</v>
       </c>
       <c r="I51" t="n">
         <v>459.4796081094204</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>7.19</v>
+        <v>4.33</v>
       </c>
       <c r="L51" t="n">
         <v>1.51</v>
@@ -3348,7 +3959,7 @@
         <v>1.51</v>
       </c>
       <c r="N51" t="n">
-        <v>2.52</v>
+        <v>3.31</v>
       </c>
       <c r="O51" t="n">
         <v>-1.01</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.06</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46275.38541666666</v>
+        <v>46275.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>450.05</v>
+        <v>448.5</v>
       </c>
       <c r="I52" t="n">
         <v>449.2458040155494</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.2</v>
+        <v>-3.54</v>
       </c>
       <c r="L52" t="n">
         <v>4.46</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3465,6 +4100,14 @@
       <c r="Q53" t="n">
         <v>61</v>
       </c>
+      <c r="R53" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5431,7 +6074,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.6</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="6">
@@ -5441,7 +6084,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -5451,7 +6094,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="8">
@@ -5461,7 +6104,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -5471,7 +6114,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.1</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="10">
@@ -5481,7 +6124,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -5491,7 +6134,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -5501,7 +6144,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -5511,7 +6154,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.7</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="14">
@@ -5521,7 +6164,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.33</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="15">
@@ -5531,7 +6174,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.32</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="16">
@@ -5541,7 +6184,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.34</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="17">
@@ -5551,7 +6194,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.14</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="18">
@@ -5561,7 +6204,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.1</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="19">
@@ -5571,7 +6214,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.73</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="20">
@@ -5581,7 +6224,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.46</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="21">
@@ -5591,7 +6234,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.09</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="22">
@@ -5601,7 +6244,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -5611,7 +6254,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -5621,7 +6264,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="25">
@@ -5641,7 +6284,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="27">
@@ -5661,7 +6304,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
